--- a/votantes/GLOBAL/13._CORDOBA/df_votantes_total_13._CORDOBA.xlsx
+++ b/votantes/GLOBAL/13._CORDOBA/df_votantes_total_13._CORDOBA.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,7 +506,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46026.8466087963</v>
+        <v>46026.85109953704</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -515,7 +515,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>50805012</t>
+          <t>50805042</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -526,45 +526,111 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
+          <t>ARGEL</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>YANEZ</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>targely@yahoo.es</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>573138290578</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>13. CORDOBA</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>058. TIERRALTA</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>99. ZONA 99</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>18. LOS MORALES</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Solamente Votante</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46026.8466087963</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C.C.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>50805012</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TERESA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ARGEL </t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>YANEZ</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>targely@yahoo.es</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>573138290548</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>13. CORDOBA</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>058. TIERRALTA</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>99. ZONA 99</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>18. LOS MORALES</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Solamente Votante</t>
         </is>

--- a/votantes/GLOBAL/13._CORDOBA/df_votantes_total_13._CORDOBA.xlsx
+++ b/votantes/GLOBAL/13._CORDOBA/df_votantes_total_13._CORDOBA.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,72 +565,6 @@
         </is>
       </c>
       <c r="N2" t="inlineStr">
-        <is>
-          <t>Solamente Votante</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>46026.8466087963</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>C.C.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>50805012</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>TERESA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ARGEL </t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>YANEZ</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>targely@yahoo.es</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>573138290548</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>13. CORDOBA</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>058. TIERRALTA</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>99. ZONA 99</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>18. LOS MORALES</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
         <is>
           <t>Solamente Votante</t>
         </is>
